--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484027_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484027_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3298</v>
+        <v>6.2909</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0011</v>
+        <v>6.0465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3286</v>
+        <v>0.2445</v>
       </c>
       <c r="G2" t="n">
         <v>3.3676</v>
@@ -610,13 +610,13 @@
         <v>3.3725</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1592</v>
+        <v>0.0751</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9401</v>
+        <v>2.5865</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4912</v>
+        <v>3.4742</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.551</v>
+        <v>-0.8877</v>
       </c>
       <c r="G3" t="n">
         <v>1.7317</v>
@@ -688,13 +688,13 @@
         <v>3.1741</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1019</v>
+        <v>0.7482</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7426</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3423</v>
+        <v>0.0056</v>
       </c>
       <c r="V3" t="n">
         <v>-2.0757</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4446</v>
+        <v>2.5282</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5727</v>
+        <v>3.516</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1281</v>
+        <v>-0.9879</v>
       </c>
       <c r="G4" t="n">
         <v>1.4238</v>
@@ -766,13 +766,13 @@
         <v>3.9677</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6321</v>
+        <v>0.7156</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1395</v>
+        <v>1.0827</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5074</v>
+        <v>-0.3671</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6032</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5443</v>
+        <v>1.6769</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8291</v>
+        <v>0.596</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2848</v>
+        <v>1.081</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4364</v>
+        <v>-4.7184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7914</v>
+        <v>0.6258</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.355</v>
+        <v>-5.3443</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6987</v>
+        <v>-2.2102</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6585</v>
+        <v>3.0306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>-5.2408</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2623</v>
+        <v>-2.5083</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8672</v>
+        <v>-2.4047</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3951</v>
+        <v>-0.1035</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5871</v>
+        <v>2.9758</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>3.9677</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0527</v>
+        <v>0.1375</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1304</v>
+        <v>0.5159</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.3785</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.532</v>
+        <v>3.2821</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7873</v>
+        <v>1.391</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2656</v>
+        <v>1.6478</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0529</v>
+        <v>-0.2568</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.7184</v>
+        <v>0.4364</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6258</v>
+        <v>0.7914</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.3443</v>
+        <v>-0.355</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.2102</v>
+        <v>1.6987</v>
       </c>
       <c r="K6" t="n">
-        <v>3.0306</v>
+        <v>1.6585</v>
       </c>
       <c r="L6" t="n">
-        <v>-5.2408</v>
+        <v>0.0402</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5083</v>
+        <v>-1.2623</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.4047</v>
+        <v>-0.8672</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1035</v>
+        <v>-0.3951</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9758</v>
+        <v>1.5871</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.9677</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7521</v>
+        <v>-0.1006</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3456</v>
+        <v>-0.051</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4065</v>
+        <v>-0.0496</v>
       </c>
       <c r="V6" t="n">
-        <v>3.2821</v>
+        <v>-0.532</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2821</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0735</v>
+        <v>0.3853</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6057</v>
+        <v>1.0365</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6792</v>
+        <v>-0.6511</v>
       </c>
       <c r="G7" t="n">
         <v>0.4568</v>
@@ -1000,13 +1000,13 @@
         <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3157</v>
+        <v>0.1431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.238</v>
+        <v>0.1927</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0496</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8199</v>
+        <v>-1.2102</v>
       </c>
       <c r="E8" t="n">
-        <v>0.677</v>
+        <v>0.3709</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4969</v>
+        <v>-1.5811</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5521</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2046</v>
+        <v>-0.1856</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4932</v>
+        <v>0.1871</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2885</v>
+        <v>-0.3727</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3993</v>
+        <v>-2.4404</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3982</v>
+        <v>-2.5796</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0011</v>
+        <v>0.1392</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9236</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1276</v>
+        <v>0.0864</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1304</v>
+        <v>-0.051</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0029</v>
+        <v>0.1374</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>D. CORTES ALEJANDRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.711</v>
+        <v>-3.0454</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1798</v>
+        <v>-5.0176</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5311</v>
+        <v>1.9722</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2595</v>
+        <v>-4.3463</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7414</v>
+        <v>-2.1269</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5182</v>
+        <v>-2.2193</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3268</v>
+        <v>-2.7561</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3268</v>
+        <v>-0.1157</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.6405</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9327</v>
+        <v>-1.5902</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4145</v>
+        <v>-2.0113</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5182</v>
+        <v>0.4211</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>2.9758</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1518</v>
+        <v>0.3089</v>
       </c>
       <c r="T10" t="n">
-        <v>0.873</v>
+        <v>0.3968</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2788</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8692</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CORTES ALEJANDRE</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4211</v>
+        <v>-3.5312</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.225</v>
+        <v>-0.8317</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8039</v>
+        <v>-2.6995</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3463</v>
+        <v>-3.2595</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1269</v>
+        <v>-2.7414</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2193</v>
+        <v>-0.5182</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7561</v>
+        <v>-0.3268</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1157</v>
+        <v>-0.3268</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6405</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5902</v>
+        <v>-2.9327</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0113</v>
+        <v>-2.4145</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4211</v>
+        <v>-0.5182</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.9919</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.9838</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.9758</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.0667</v>
+        <v>0.3316</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8105</v>
+        <v>0.2211</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2562</v>
+        <v>0.1105</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6745</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.006500000000001</v>
+        <v>-7.4581</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6179</v>
+        <v>-5.2098</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3886</v>
+        <v>-2.2483</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5319</v>
@@ -1390,13 +1390,13 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8361</v>
+        <v>-0.2877</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1133</v>
+        <v>0.2948</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7227</v>
+        <v>-0.5824</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3852</v>
+        <v>-2.826499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4903</v>
+        <v>3.0492</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.875399999999999</v>
+        <v>-5.875500000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-12.9155</v>
@@ -1447,7 +1447,7 @@
         <v>11.9259</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.276200000000001</v>
+        <v>-4.2762</v>
       </c>
       <c r="M13" t="n">
         <v>-20.5656</v>
@@ -1459,7 +1459,7 @@
         <v>-2.4933</v>
       </c>
       <c r="P13" t="n">
-        <v>9.919199999999996</v>
+        <v>9.919199999999998</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.8868</v>
@@ -1468,13 +1468,13 @@
         <v>23.8061</v>
       </c>
       <c r="S13" t="n">
-        <v>1.219</v>
+        <v>2.7774</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7783</v>
+        <v>4.3367</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5593</v>
+        <v>-1.5592</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6078</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6849</v>
+        <v>4.0453</v>
       </c>
       <c r="E14" t="n">
         <v>1.6687</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0162</v>
+        <v>2.3766</v>
       </c>
       <c r="G14" t="n">
         <v>3.4955</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6836</v>
+        <v>-0.3231</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0679</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6156</v>
+        <v>-0.2551</v>
       </c>
       <c r="V14" t="n">
         <v>0.6745</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8957</v>
+        <v>2.4773</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6419</v>
+        <v>2.152</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2538</v>
+        <v>0.3253</v>
       </c>
       <c r="G15" t="n">
         <v>2.3916</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7347</v>
+        <v>-0.1531</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6858</v>
+        <v>-0.1757</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0489</v>
+        <v>0.0226</v>
       </c>
       <c r="V15" t="n">
         <v>3.0162</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7779</v>
+        <v>2.3544</v>
       </c>
       <c r="E16" t="n">
-        <v>1.293</v>
+        <v>1.7012</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4849</v>
+        <v>0.6532</v>
       </c>
       <c r="G16" t="n">
         <v>3.9597</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8174</v>
+        <v>-0.2409</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1939</v>
+        <v>-0.0256</v>
       </c>
       <c r="V16" t="n">
         <v>1.8097</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.716</v>
+        <v>1.4459</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3576</v>
+        <v>1.6029</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3584</v>
+        <v>-0.157</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6118</v>
+        <v>0.6742</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.6702</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6144</v>
+        <v>0.0039</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0827</v>
+        <v>1.189</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3171</v>
+        <v>1.0686</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.1205</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4709</v>
+        <v>-0.5149</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.3196</v>
+        <v>-0.3983</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8487</v>
+        <v>-0.1165</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.5709</v>
+        <v>1.5871</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.3564</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5399</v>
+        <v>0.3911</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2301</v>
+        <v>0.4138</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3098</v>
+        <v>-0.0227</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1352</v>
+        <v>-1.2065</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4012</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7078</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.113</v>
+        <v>0.7454</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4052</v>
+        <v>0.0413</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6742</v>
+        <v>2.6118</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6702</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0039</v>
+        <v>1.6144</v>
       </c>
       <c r="J18" t="n">
-        <v>1.189</v>
+        <v>4.0827</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0686</v>
+        <v>3.3171</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5149</v>
+        <v>-1.4709</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3983</v>
+        <v>-2.3196</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1165</v>
+        <v>0.8487</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5871</v>
+        <v>-3.5709</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-5.3564</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.653</v>
+        <v>0.6107</v>
       </c>
       <c r="T18" t="n">
-        <v>0.924</v>
+        <v>0.6179</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.271</v>
+        <v>-0.0073</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2065</v>
+        <v>1.1352</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4012</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. IDOM</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6754</v>
+        <v>0.0752</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9077</v>
+        <v>-0.0839</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5831</v>
+        <v>0.1591</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8606</v>
+        <v>-0.1841</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3884</v>
+        <v>-1.402</v>
       </c>
       <c r="I19" t="n">
-        <v>1.249</v>
+        <v>1.2178</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2887</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6034</v>
+        <v>0.3226</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6853</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4281</v>
+        <v>-1.1544</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9917</v>
+        <v>-1.7245</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5637</v>
+        <v>0.5702</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3806</v>
+        <v>-1.1903</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2148</v>
+        <v>0.0609</v>
       </c>
       <c r="T19" t="n">
-        <v>0.924</v>
+        <v>0.1361</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1388</v>
+        <v>-0.0752</v>
       </c>
       <c r="V19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>J. MIRANDA VARGAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7096</v>
+        <v>-0.2234</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.288</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4216</v>
+        <v>0.6914</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1841</v>
+        <v>0.9202</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.402</v>
+        <v>0.7103</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2178</v>
+        <v>0.2099</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.2958</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3226</v>
+        <v>1.371</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6477000000000001</v>
+        <v>-0.0752</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1544</v>
+        <v>-0.3756</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7245</v>
+        <v>-0.6607</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5702</v>
+        <v>0.2851</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R20" t="n">
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7238</v>
+        <v>-0.35</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0679</v>
+        <v>-0.0283</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6559</v>
+        <v>-0.3217</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MIRANDA VARGAS</t>
+          <t>J. IDOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.615</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3229</v>
+        <v>2.4996</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4151</v>
+        <v>-3.1146</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9202</v>
+        <v>0.8606</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7103</v>
+        <v>-0.3884</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2099</v>
+        <v>1.249</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2958</v>
+        <v>2.2887</v>
       </c>
       <c r="K21" t="n">
-        <v>1.371</v>
+        <v>1.6034</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0752</v>
+        <v>0.6853</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3756</v>
+        <v>-1.4281</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6607</v>
+        <v>-1.9917</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2851</v>
+        <v>0.5637</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1822</v>
+        <v>-2.3806</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0344</v>
+        <v>-0.1545</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4364</v>
+        <v>0.5159</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.598</v>
+        <v>-0.6704</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1045</v>
+        <v>-3.9208</v>
       </c>
       <c r="E22" t="n">
         <v>-3.4955</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6089</v>
+        <v>-0.4252</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8139</v>
@@ -2170,13 +2170,13 @@
         <v>2.3806</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.9806</v>
       </c>
       <c r="T22" t="n">
         <v>0.3629</v>
       </c>
       <c r="U22" t="n">
-        <v>0.434</v>
+        <v>0.6177</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0874</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.385</v>
+        <v>6.425700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>5.875499999999999</v>
+        <v>5.8756</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4904</v>
+        <v>0.5501000000000003</v>
       </c>
       <c r="G23" t="n">
         <v>12.9156</v>
@@ -2227,7 +2227,7 @@
         <v>18.0722</v>
       </c>
       <c r="L23" t="n">
-        <v>2.493300000000001</v>
+        <v>2.4933</v>
       </c>
       <c r="M23" t="n">
         <v>-7.649800000000001</v>
@@ -2248,22 +2248,22 @@
         <v>13.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2189</v>
+        <v>0.8217000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5595</v>
+        <v>1.5594</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.7783</v>
+        <v>-0.7376999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>2.6077</v>
+        <v>2.607700000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>7.557</v>
+        <v>7.556999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.9493</v>
+        <v>-4.949300000000001</v>
       </c>
     </row>
   </sheetData>
